--- a/data/trans_camb/P8_2_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P8_2_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 6,47</t>
+          <t>-5,71; 6,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 8,22</t>
+          <t>-4,07; 8,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 4,59</t>
+          <t>-6,53; 5,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 14,79</t>
+          <t>0,78; 15,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 15,0</t>
+          <t>1,01; 15,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 6,77</t>
+          <t>-5,46; 6,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 8,66</t>
+          <t>-0,74; 8,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 10,29</t>
+          <t>0,41; 10,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 3,67</t>
+          <t>-4,46; 3,92</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 51,57</t>
+          <t>-30,33; 55,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 66,96</t>
+          <t>-22,2; 66,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,11; 38,85</t>
+          <t>-35,2; 45,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 100,76</t>
+          <t>3,78; 102,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 96,95</t>
+          <t>4,48; 100,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 46,09</t>
+          <t>-24,2; 46,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 59,02</t>
+          <t>-4,09; 60,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 68,79</t>
+          <t>0,31; 67,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-22,87; 24,0</t>
+          <t>-22,48; 27,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 6,21</t>
+          <t>-2,71; 6,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 2,65</t>
+          <t>-5,97; 2,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 9,81</t>
+          <t>-0,46; 9,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 7,29</t>
+          <t>-4,24; 6,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 2,49</t>
+          <t>-7,93; 2,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 4,67</t>
+          <t>-5,0; 5,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 4,78</t>
+          <t>-2,35; 4,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 0,93</t>
+          <t>-5,99; 1,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 6,09</t>
+          <t>-1,29; 5,91</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 53,76</t>
+          <t>-19,13; 54,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,66; 24,31</t>
+          <t>-38,79; 21,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 86,57</t>
+          <t>-3,68; 79,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 32,03</t>
+          <t>-16,0; 30,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,08; 11,51</t>
+          <t>-29,39; 9,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 21,19</t>
+          <t>-17,9; 23,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 27,21</t>
+          <t>-11,48; 28,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 5,28</t>
+          <t>-28,18; 5,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 36,03</t>
+          <t>-6,13; 34,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 9,93</t>
+          <t>-0,78; 10,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 6,19</t>
+          <t>-3,37; 6,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 7,71</t>
+          <t>-1,78; 7,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 4,31</t>
+          <t>-8,82; 4,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 0,28</t>
+          <t>-13,12; -0,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,04; -0,88</t>
+          <t>-12,31; -0,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 5,17</t>
+          <t>-3,08; 5,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,66</t>
+          <t>-6,85; 1,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 2,13</t>
+          <t>-5,78; 1,82</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 104,84</t>
+          <t>-7,77; 112,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 63,39</t>
+          <t>-24,63; 74,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 83,15</t>
+          <t>-13,66; 88,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 20,6</t>
+          <t>-30,71; 22,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,29; 1,14</t>
+          <t>-45,68; -1,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,67; -4,52</t>
+          <t>-41,64; -3,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 31,58</t>
+          <t>-15,32; 31,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 10,46</t>
+          <t>-33,29; 8,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,45; 13,7</t>
+          <t>-28,0; 10,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 8,4</t>
+          <t>-2,23; 8,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 7,23</t>
+          <t>-2,67; 8,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 12,0</t>
+          <t>-0,07; 11,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 14,19</t>
+          <t>1,39; 14,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 9,61</t>
+          <t>-3,19; 9,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 0,49</t>
+          <t>-13,68; 0,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 9,43</t>
+          <t>1,37; 9,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 6,8</t>
+          <t>-1,41; 7,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,04</t>
+          <t>-6,1; 4,34</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 79,26</t>
+          <t>-14,58; 77,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 65,48</t>
+          <t>-18,78; 76,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 112,81</t>
+          <t>-2,44; 111,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,01; 68,31</t>
+          <t>4,59; 70,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 46,9</t>
+          <t>-13,5; 47,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,21; 1,16</t>
+          <t>-55,35; 2,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,21; 57,91</t>
+          <t>6,97; 63,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 40,87</t>
+          <t>-6,85; 45,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 25,0</t>
+          <t>-31,11; 26,25</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,6; 14,58</t>
+          <t>1,34; 15,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 8,77</t>
+          <t>-2,22; 8,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 7,42</t>
+          <t>-2,5; 7,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 20,25</t>
+          <t>3,37; 20,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 11,16</t>
+          <t>-4,42; 11,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 11,22</t>
+          <t>-9,65; 11,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,58; 16,02</t>
+          <t>5,07; 15,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 8,13</t>
+          <t>-1,5; 8,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 8,59</t>
+          <t>-2,6; 8,68</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,43; 205,2</t>
+          <t>7,38; 231,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 133,47</t>
+          <t>-19,33; 141,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 111,43</t>
+          <t>-20,59; 119,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16,53; 141,34</t>
+          <t>14,26; 135,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 79,42</t>
+          <t>-19,08; 83,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,68; 71,15</t>
+          <t>-39,21; 74,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,48; 144,44</t>
+          <t>28,1; 133,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 72,66</t>
+          <t>-9,82; 70,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 69,24</t>
+          <t>-13,45; 72,98</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 10,97</t>
+          <t>-2,04; 10,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 11,82</t>
+          <t>-1,24; 11,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 2,63</t>
+          <t>-8,26; 2,58</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 9,75</t>
+          <t>-4,59; 10,25</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 11,58</t>
+          <t>-3,03; 11,98</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,92; -0,17</t>
+          <t>-12,28; 0,7</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 8,39</t>
+          <t>-1,4; 7,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 9,75</t>
+          <t>-0,4; 10,1</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-8,9; -0,28</t>
+          <t>-8,82; -0,83</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 90,26</t>
+          <t>-12,45; 87,53</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 100,51</t>
+          <t>-7,02; 95,99</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,16; 23,28</t>
+          <t>-42,22; 22,36</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 44,31</t>
+          <t>-15,52; 50,86</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 51,73</t>
+          <t>-10,06; 54,8</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-42,82; -0,11</t>
+          <t>-41,34; 3,95</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 46,39</t>
+          <t>-5,73; 43,78</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 53,18</t>
+          <t>-2,35; 54,42</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-37,2; -1,52</t>
+          <t>-37,76; -4,35</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 1,15</t>
+          <t>-6,72; 1,14</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,2</t>
+          <t>-3,43; 4,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,23</t>
+          <t>-3,06; 5,25</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 7,03</t>
+          <t>-2,92; 6,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 5,02</t>
+          <t>-5,0; 4,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 3,48</t>
+          <t>-14,33; 3,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 2,98</t>
+          <t>-3,32; 3,01</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,92</t>
+          <t>-2,62; 3,78</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 2,58</t>
+          <t>-8,13; 2,64</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 8,23</t>
+          <t>-37,6; 8,86</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 38,17</t>
+          <t>-20,08; 33,89</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 38,84</t>
+          <t>-17,92; 39,37</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 32,99</t>
+          <t>-12,31; 31,4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 24,47</t>
+          <t>-19,49; 21,05</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-59,53; 16,06</t>
+          <t>-59,23; 15,35</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 16,5</t>
+          <t>-16,05; 17,15</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 21,89</t>
+          <t>-12,39; 21,13</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 14,29</t>
+          <t>-37,8; 14,1</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 5,44</t>
+          <t>-2,22; 5,1</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 0,89</t>
+          <t>-5,57; 1,02</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 55,42</t>
+          <t>-2,51; 56,97</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 3,09</t>
+          <t>-5,63; 3,1</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 0,28</t>
+          <t>-8,1; 0,44</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 4,7</t>
+          <t>-3,27; 5,05</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,88</t>
+          <t>-2,81; 2,89</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,95; -0,42</t>
+          <t>-6,1; -0,56</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 37,15</t>
+          <t>-1,42; 37,77</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 43,47</t>
+          <t>-13,87; 40,83</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-35,91; 7,05</t>
+          <t>-33,84; 7,88</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 417,29</t>
+          <t>-17,0; 460,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-20,13; 14,79</t>
+          <t>-21,69; 15,07</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 1,57</t>
+          <t>-31,73; 2,29</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 23,09</t>
+          <t>-12,98; 23,27</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 16,32</t>
+          <t>-13,71; 16,36</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-29,32; -2,5</t>
+          <t>-29,75; -2,86</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 194,24</t>
+          <t>-7,63; 204,82</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,48</t>
+          <t>-0,18; 3,24</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,32</t>
+          <t>-1,03; 2,44</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,72; 24,28</t>
+          <t>0,84; 25,28</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,56</t>
+          <t>0,34; 4,55</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,64</t>
+          <t>-2,45; 1,52</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,41; -0,03</t>
+          <t>-6,76; -0,08</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,37</t>
+          <t>0,68; 3,46</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,38</t>
+          <t>-1,31; 1,45</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 13,18</t>
+          <t>-1,1; 11,53</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 26,39</t>
+          <t>-1,09; 25,29</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 17,95</t>
+          <t>-6,91; 18,88</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5,08; 178,12</t>
+          <t>5,74; 192,07</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1,4; 20,51</t>
+          <t>1,45; 20,33</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 7,44</t>
+          <t>-9,98; 6,92</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-26,98; -0,79</t>
+          <t>-28,14; -0,65</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,42; 19,11</t>
+          <t>3,23; 18,94</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 7,71</t>
+          <t>-6,77; 7,95</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 72,82</t>
+          <t>-5,77; 63,55</t>
         </is>
       </c>
     </row>
